--- a/decks/dogizone/keyword-research.xlsx
+++ b/decks/dogizone/keyword-research.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,13 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +58,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CC53F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001797d6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0046AE41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006b4c9a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B942"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000e6e2e"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -92,6 +127,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,57 +533,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Article Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Primary Keyword</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -550,12 +609,12 @@
       <c r="E2" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -580,49 +639,48 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>What Is French Ring? Everything You Need to Know Before Starting</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>what is french ring dog sport</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -644,12 +702,12 @@
       <c r="E4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -674,49 +732,48 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>How to Train for French Ring: Beginner's Step-by-Step Guide</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>french ring training</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -738,12 +795,12 @@
       <c r="E6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -763,49 +820,48 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>French Ring Dog Sport Near Me: How to Find a Club</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>french ring dog sport near me</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -827,12 +883,12 @@
       <c r="E8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -857,49 +913,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Dog Daycare Rockville MD: A Day in the Life at DogiZone</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>dog daycare rockville md</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -921,12 +976,12 @@
       <c r="E10" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -951,49 +1006,48 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Dog Daycare Near Me: What to Look for Before You Book</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>dog daycare near me</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1015,12 +1069,12 @@
       <c r="E12" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -1045,49 +1099,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Dog Separation Anxiety: Causes, Signs, and How Daycare Helps</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>dog separation anxiety</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bridges training content to daycare conversion.</t>
         </is>
@@ -1113,12 +1167,12 @@
       <c r="E14" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -1138,49 +1192,48 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Dog Daycare vs Dog Walker: Which Is Better for Your Dog's Day?</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>dog daycare vs dog walker</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1202,12 +1255,12 @@
       <c r="E16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -1227,49 +1280,48 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>French Ring Equipment List: Gear You Need to Get Started</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>french ring equipment</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1291,12 +1343,12 @@
       <c r="E18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -1316,49 +1368,48 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Luxury Dog Boarding vs Standard: What's Actually Different?</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>luxury dog boarding</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1380,12 +1431,12 @@
       <c r="E20" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -1410,49 +1461,49 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>What to Pack for Dog Boarding: A Complete Checklist</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>what to pack for dog boarding</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -1478,12 +1529,12 @@
       <c r="E22" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1503,49 +1554,49 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Belgian Malinois Training Guide: From Puppy to Working Dog</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>belgian malinois training</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>High volume — most French Ring dogs are Malinois.</t>
         </is>
@@ -1571,12 +1622,12 @@
       <c r="E24" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -1596,49 +1647,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>How Long Can You Leave a Dog Home Alone? (Honest Answer)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>how long can you leave a dog alone</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>AEO format — bridges to daycare need.</t>
         </is>
@@ -1664,12 +1715,12 @@
       <c r="E26" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -1694,49 +1745,48 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Dog Boarding Gaithersburg MD: Nearby Options Compared</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>dog boarding gaithersburg md</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1758,12 +1808,12 @@
       <c r="E28" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1783,49 +1833,49 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Can Aggressive Dogs Go to Daycare? (What Facilities Actually Check)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>aggressive dog daycare</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>AEO + bridges French Ring sport dogs to boarding.</t>
         </is>
@@ -1851,12 +1901,12 @@
       <c r="E30" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -1881,49 +1931,48 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Dog Training Rockville MD: Obedience, Sport, and Behavior</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>dog training rockville md</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1945,12 +1994,12 @@
       <c r="E32" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -1970,49 +2019,48 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Dog Boarding Bethesda MD: Service Guide</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>dog boarding bethesda md</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2034,12 +2082,12 @@
       <c r="E34" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2059,49 +2107,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>How Daycare Reduces Destructive Behavior in High-Energy Dogs</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>dog daycare reduce destructive behavior</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Bridges behavior content to daycare conversion.</t>
         </is>
@@ -2127,12 +2175,12 @@
       <c r="E36" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -2157,49 +2205,48 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Dog Boarding Silver Spring MD: Options and What to Expect</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>dog boarding silver spring md</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2221,12 +2268,12 @@
       <c r="E38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2246,49 +2293,49 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>How to Transition a Dog to Daycare: First Visit Tips</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>dog first day daycare</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -2314,12 +2361,12 @@
       <c r="E40" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -2344,49 +2391,48 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Dog Boarding Washington DC: Metro Area Options Guide</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>dog boarding washington dc</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2408,12 +2454,12 @@
       <c r="E42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -2433,49 +2479,48 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Malinois vs German Shepherd for French Ring: Which Excels?</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>malinois vs german shepherd french ring</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2497,12 +2542,12 @@
       <c r="E44" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2522,49 +2567,48 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Dog Daycare Potomac MD: Service Guide for Potomac Residents</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>dog daycare potomac md</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2586,12 +2630,12 @@
       <c r="E46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -2611,49 +2655,49 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Dog Boarding Holiday: How to Book for Peak Season</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>dog boarding holiday</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="J47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Seasonal urgency.</t>
         </is>
@@ -2679,12 +2723,12 @@
       <c r="E48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -2709,49 +2753,49 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Belgian Malinois Boarding: Special Considerations for High-Drive Dogs</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>belgian malinois boarding</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Bridges French Ring audience to boarding conversion.</t>
         </is>
@@ -2777,12 +2821,12 @@
       <c r="E50" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -2802,49 +2846,48 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Puppy Socialization Classes Near Me: What to Look For</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>puppy socialization classes near me</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2866,12 +2909,12 @@
       <c r="E52" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -2896,49 +2939,49 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>How Many Days a Week Should a Dog Go to Daycare?</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>how often should dog go to daycare</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="J53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -2964,12 +3007,12 @@
       <c r="E54" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -2989,49 +3032,49 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Dutch Shepherd Training and Sport: How It Compares to Belgian Malinois</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>dutch shepherd training sport</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="J55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>French Ring-adjacent — Dutch Shepherds are common sport dogs.</t>
         </is>
@@ -3057,12 +3100,12 @@
       <c r="E56" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -3082,49 +3125,48 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Dog Boarding Kensington MD: Service Guide</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>dog boarding kensington md</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3146,12 +3188,12 @@
       <c r="E58" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3171,49 +3213,48 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Dog Boarding Germantown MD: Guide for Germantown Pet Owners</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>dog boarding germantown md</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3235,12 +3276,12 @@
       <c r="E60" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -3265,49 +3306,48 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Dog Grooming Guide: How Often Does Your Breed Need Grooming?</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>how often dog grooming</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3329,12 +3369,12 @@
       <c r="E62" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -3354,49 +3394,49 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>French Ring Puppy Selection: What to Look for at 8 Weeks</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>french ring puppy selection</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Attracts sport dog enthusiasts early in their journey.</t>
         </is>
@@ -3422,12 +3462,12 @@
       <c r="E64" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -3452,49 +3492,48 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Dog Boarding McLean VA: Options for Northern Virginia Owners</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>dog boarding mclean va</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3516,12 +3555,12 @@
       <c r="E66" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3541,49 +3580,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Dog Health Screening for Boarding: What Facilities Should Check</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>dog boarding health requirements</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Trust content.</t>
         </is>
@@ -3609,12 +3648,12 @@
       <c r="E68" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -3639,49 +3678,48 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Senior Dog Boarding: Special Care for Older Dogs</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>senior dog boarding</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="J69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3703,12 +3741,12 @@
       <c r="E70" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -3728,49 +3766,48 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Dog Training Classes Near Me: Group vs Private Lessons</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>dog training classes near me</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J71" s="4" t="n">
+      <c r="J71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3792,12 +3829,12 @@
       <c r="E72" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -3817,49 +3854,49 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>French Ring Ring 1 Trial: Full Breakdown of What's Tested</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>french ring ring 1 trial</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="J73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Authority depth content.</t>
         </is>
@@ -3885,12 +3922,12 @@
       <c r="E74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -3915,49 +3952,49 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>DogiZone vs Other Rockville Dog Boarding: An Honest Comparison</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>dogizone rockville review</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Branded</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Reputation content — captures branded review queries.</t>
         </is>
@@ -3983,12 +4020,12 @@
       <c r="E76" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -4008,49 +4045,49 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Dog Boarding for Christmas and Thanksgiving: How to Book Early</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>dog boarding christmas</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J77" s="4" t="n">
+      <c r="J77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Seasonal — high booking-intent search.</t>
         </is>
@@ -4076,12 +4113,12 @@
       <c r="E78" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -4101,49 +4138,49 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Working Dog Breeds: Training Needs and Exercise Requirements</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>working dog breeds training</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J79" s="4" t="n">
+      <c r="J79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Attracts French Ring / sport dog audience.</t>
         </is>
@@ -4169,12 +4206,12 @@
       <c r="E80" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4194,49 +4231,49 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>What Is Dog Temperament Testing? How DogiZone Evaluates New Dogs</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>dog temperament testing boarding</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="J81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Trust differentiator.</t>
         </is>
@@ -4262,12 +4299,12 @@
       <c r="E82" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4287,49 +4324,48 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Off-Leash Dog Play: Benefits, Risks, and What Daycare Facilities Should Ensure</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>off leash dog play safety</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -4351,12 +4387,12 @@
       <c r="E84" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -4381,49 +4417,48 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Positive Reinforcement Dog Training: The Complete Guide</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>positive reinforcement dog training</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="J85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -4445,12 +4480,12 @@
       <c r="E86" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4470,49 +4505,48 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Dog Daycare Fairfax VA: Full-Day Care for Working Dog Owners</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>dog daycare fairfax va</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -4534,12 +4568,12 @@
       <c r="E88" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -4564,49 +4598,48 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>French Ring Jump Exercises: Building Height and Confidence</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>french ring jump exercises</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="J89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -4628,12 +4661,12 @@
       <c r="E90" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -4658,49 +4691,48 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Dog Boarding Herndon VA: Options for Herndon Pet Owners</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>dog boarding herndon va</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="J91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -4722,12 +4754,12 @@
       <c r="E92" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -4752,49 +4784,49 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>What Shots Does a Dog Need for Boarding?</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>what shots does dog need for boarding</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="J93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>AEO format — very common question.</t>
         </is>
@@ -4820,12 +4852,12 @@
       <c r="E94" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4845,49 +4877,49 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>French Ring Training Drills: Week-by-Week Schedule for Beginners</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>french ring training drills</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J95" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>High engagement content for sport dog community.</t>
         </is>
@@ -4913,12 +4945,12 @@
       <c r="E96" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -4943,49 +4975,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Dog Daycare for High-Energy Dogs: Why Standard Daycares Fail Them</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>dog daycare high energy dogs</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Bridges French Ring sport dog niche to daycare audience.</t>
         </is>
@@ -5011,12 +5043,12 @@
       <c r="E98" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -5036,49 +5068,48 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Dog Boarding Reston VA: Service Guide for Reston Pet Owners</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>dog boarding reston va</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -5100,12 +5131,12 @@
       <c r="E100" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -5130,49 +5161,48 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Dog Boarding Camp: What It Is and Who It's For</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>dog boarding camp</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n">
+      <c r="J101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -5194,12 +5224,12 @@
       <c r="E102" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -5224,49 +5254,48 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Dog Boarding Chantilly VA: Service Guide for Chantilly Pet Owners</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>dog boarding chantilly va</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -5288,12 +5317,12 @@
       <c r="E104" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -5311,52 +5340,50 @@
       <c r="J104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Dog Boarding Leesburg VA: Service Guide for Loudoun County</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>dog boarding leesburg va</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n">
+      <c r="J105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -5378,12 +5405,12 @@
       <c r="E106" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -5401,52 +5428,50 @@
       <c r="J106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Dog Boarding Ashburn VA: Options for Ashburn Pet Owners</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>dog boarding ashburn va</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J107" s="4" t="n">
+      <c r="J107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -5468,12 +5493,12 @@
       <c r="E108" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -5491,52 +5516,50 @@
       <c r="J108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Dog Boarding Rockville vs Home Dog Sitter: Which Is Better?</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>dog boarding vs home dog sitter</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -5558,12 +5581,12 @@
       <c r="E110" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -5581,52 +5604,50 @@
       <c r="J110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Dog Boarding Columbia MD: Howard County Service Guide</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>dog boarding columbia md</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J111" s="4" t="n">
+      <c r="J111" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5648,12 +5669,12 @@
       <c r="E112" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -5671,52 +5692,50 @@
       <c r="J112" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Dog Boarding Frederick MD: Service Guide for Frederick County</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>dog boarding frederick md</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
+      <c r="J113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -5738,12 +5757,12 @@
       <c r="E114" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -5761,52 +5780,50 @@
       <c r="J114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Puppy Board and Train: Is It Worth It?</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>puppy board and train program</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G115" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J115" s="4" t="n">
+      <c r="J115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5828,12 +5845,12 @@
       <c r="E116" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5851,52 +5868,50 @@
       <c r="J116" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Dog Boarding Waldorf MD: Southern Maryland Service Guide</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>dog boarding waldorf md</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
+      <c r="J117" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5918,12 +5933,12 @@
       <c r="E118" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -5941,52 +5956,50 @@
       <c r="J118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>French Ring Sleeve Work: Building Drive and Grip Properly</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>french ring sleeve training</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J119" s="4" t="n">
+      <c r="J119" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -6008,12 +6021,12 @@
       <c r="E120" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -6031,52 +6044,50 @@
       <c r="J120" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Dog Boarding Annapolis MD: Service Guide for Anne Arundel County</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>dog boarding annapolis md</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
+      <c r="J121" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6103,42 +6114,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>In Plan?</t>
         </is>
@@ -6156,12 +6167,12 @@
       <c r="C2" t="n">
         <v>32</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -6183,38 +6194,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>dog daycare near me</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>27100</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>30</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6232,12 +6243,12 @@
       <c r="C4" t="n">
         <v>22</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -6259,38 +6270,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dog training classes near me</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>22200</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6308,12 +6319,12 @@
       <c r="C6" t="n">
         <v>24</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -6335,38 +6346,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>dog boarding rockville md</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>1300</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6384,12 +6395,12 @@
       <c r="C8" t="n">
         <v>18</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -6411,38 +6422,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>french ring vs schutzhund</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" t="n">
         <v>1300</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6460,12 +6471,12 @@
       <c r="C10" t="n">
         <v>26</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Dog Training &amp; Behavior</t>
         </is>
@@ -6487,38 +6498,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>dog boarding bethesda md</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" t="n">
         <v>880</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" t="n">
         <v>16</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6536,12 +6547,12 @@
       <c r="C12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -6563,38 +6574,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dog boarding washington dc</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" t="n">
         <v>4400</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" t="n">
         <v>22</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6612,12 +6623,12 @@
       <c r="C14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
@@ -6639,38 +6650,38 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>kennel cough boarding</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" t="n">
         <v>3600</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Dog Boarding &amp; Daycare</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6688,12 +6699,12 @@
       <c r="C16" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>French Ring Sport</t>
         </is>
@@ -6736,27 +6747,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Reason Category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Why We Excluded It</t>
         </is>
@@ -6786,23 +6797,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>vet near me</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>110000</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Wrong category</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Veterinary service — different competitive set. Creates confusion about DogiZone's offerings.</t>
         </is>
@@ -6832,23 +6843,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dog breeders near me</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>18100</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Wrong intent</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Breeder search — not aligned with boarding/training audience.</t>
         </is>
@@ -6878,23 +6889,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>how to train dog to attack</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>2900</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Brand risk</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Attack-training queries attract wrong audience and create liability signals.</t>
         </is>
